--- a/output/full_scan/batch_seq7_2026-10-19.xlsx
+++ b/output/full_scan/batch_seq7_2026-10-19.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>830.8885209588747</v>
+        <v>1000.888520958875</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>34.75</v>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>58.31929061825556</v>
+        <v>58.3192906523762</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>23.59557178268508</v>
+        <v>23.5955717867403</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1.788727921344796</v>
@@ -574,27 +574,27 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, williams_r_recovery, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, williams_r_recovery, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6811</v>
+        <v>6532</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>宏碁資訊</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>803.3904282968136</v>
+        <v>963.6117130647556</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>274</v>
+        <v>124</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>60.6329496121216</v>
+        <v>63.82733083899883</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>41.70655995960674</v>
+        <v>46.11251506661134</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.7581113739090873</v>
+        <v>1.546408985120026</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>1.643876022932764</v>
+        <v>0.7119880283788174</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6548</v>
+        <v>6811</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>宏碁資訊</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>790.90137418619</v>
+        <v>943.3904282968136</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>80.90000000000001</v>
+        <v>274</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,49 +658,49 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>57.29570100538789</v>
+        <v>60.63294972129266</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>29.16892821756925</v>
+        <v>41.7065599893556</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.7484488900520038</v>
+        <v>0.7581113739090873</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.6337028796701238</v>
+        <v>1.643876022692401</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6532</v>
+        <v>6526</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>763.6117130647556</v>
+        <v>911.3864579178828</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>124</v>
+        <v>781</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,49 +711,49 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>63.82733086246274</v>
+        <v>56.18481050298976</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>46.11251500075449</v>
+        <v>33.75405880725599</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.546408985120026</v>
+        <v>0.5303800440549816</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.7119880279221622</v>
+        <v>-9.792217240342019</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6706</v>
+        <v>6782</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>視陽</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>706.2820670086463</v>
+        <v>907.1543389631396</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>143</v>
+        <v>254</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,13 +764,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>48.79165728852277</v>
+        <v>60.42789567130585</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45.46393120650777</v>
+        <v>27.07664668095</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.2924112172438409</v>
+        <v>1.152009221586678</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-1.979448881210104</v>
+        <v>1.54201706621949</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6834</v>
+        <v>6548</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>天二科技</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>701.2655830013466</v>
+        <v>905.90137418619</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>133.5</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,49 +817,49 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>55.4511020046338</v>
+        <v>57.29570099317444</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>50.87543437970751</v>
+        <v>29.16892817343573</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.6620833419162628</v>
+        <v>0.7484488900520038</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.9646205764153351</v>
+        <v>0.6337028798143329</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6538</v>
+        <v>6505</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>倉和</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>687.4128541243035</v>
+        <v>886.7076207798768</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>297</v>
+        <v>116</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>45.27389891271131</v>
+        <v>65.28809820082981</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>30.67020471640325</v>
+        <v>62.95132622580619</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.9918131264981288</v>
+        <v>1.828054017062253</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-12.95897797912582</v>
+        <v>1.342616816003831</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6708</v>
+        <v>6491</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>天擎</t>
+          <t>晶碩</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>686.8160787271797</v>
+        <v>858.1217670856637</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>60.5</v>
+        <v>408.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,49 +923,49 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>57.586673573516</v>
+        <v>54.63132239663411</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>28.60303709136307</v>
+        <v>30.03275394993003</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.8302587811262123</v>
+        <v>0.7165139568369674</v>
       </c>
       <c r="K9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L9" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-0.7845188953455295</v>
+        <v>-1.271727333941016</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6505</v>
+        <v>6756</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>686.7076207798768</v>
+        <v>844</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>65.28809820273656</v>
+        <v>82.22934489342079</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>62.95132618453104</v>
+        <v>18.12173315087585</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.828054017062253</v>
+        <v>8.564569941058712</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>1.342616816148034</v>
+        <v>2.033648281642392</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6782</v>
+        <v>6538</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>視陽</t>
+          <t>倉和</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>672.1543389631396</v>
+        <v>827.4128541243035</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>254</v>
+        <v>297</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>60.42789567130585</v>
+        <v>45.27389891307806</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>27.07664665868951</v>
+        <v>30.67020472652733</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.152009221586678</v>
+        <v>0.9918131264981288</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>1.542017065979141</v>
+        <v>-12.95897797898159</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6658</v>
+        <v>6645</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>金萬林-創</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>660.0226363211235</v>
+        <v>770.2237865641223</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>201.5</v>
+        <v>14.3</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>59.31182313781227</v>
+        <v>59.60030402862489</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>37.39939293665269</v>
+        <v>30.72972216673022</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.8688446598253142</v>
+        <v>0.8223786564122251</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.0496644804133135</v>
+        <v>0.2007454826980692</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6526</v>
+        <v>6668</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>656.3864579178828</v>
+        <v>761.2184607088543</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>781</v>
+        <v>61.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>56.18481049971913</v>
+        <v>64.67619759943025</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>33.7540588086692</v>
+        <v>56.44613391250201</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.5303800440549816</v>
+        <v>1.284939289382922</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-9.792217242505217</v>
+        <v>1.350230304404018</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6756</v>
+        <v>6517</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>644</v>
+        <v>759</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>121</v>
+        <v>74.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>82.22934487422944</v>
+        <v>62.84350907903018</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>18.12173316870077</v>
+        <v>23.91494046335654</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>8.564569941058712</v>
+        <v>5.393906966793604</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>2.033648281594325</v>
+        <v>1.163693839326758</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6672</v>
+        <v>6689</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>643.5395544937039</v>
+        <v>757.3530281812483</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>562</v>
+        <v>69.2</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>69.07846657516868</v>
+        <v>63.71361924348534</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>60.10415419366847</v>
+        <v>28.30005046830126</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.054395987338452</v>
+        <v>6.062678370377307</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>11.65918524903441</v>
+        <v>0.495434857331447</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6667</v>
+        <v>6672</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>640.3494636238507</v>
+        <v>748.5395544937039</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>260</v>
+        <v>562</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,49 +1294,49 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>50.52620981609844</v>
+        <v>69.0784665907168</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>38.86354701734814</v>
+        <v>60.10415417456643</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.537563030619216</v>
+        <v>1.054395987338452</v>
       </c>
       <c r="K16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="L16" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-1.531935498023621</v>
+        <v>11.65918524884215</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6715</v>
+        <v>6706</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>嘉基</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>609.8318611344112</v>
+        <v>726.2820670086463</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>480.5</v>
+        <v>143</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>54.77367477991141</v>
+        <v>48.79165728996586</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>31.86263223108423</v>
+        <v>45.46393119223809</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.9196188655080628</v>
+        <v>0.2924112172438409</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.8597318574979838</v>
+        <v>-1.979448880969773</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6510</v>
+        <v>6715</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>嘉基</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>606.2123312282267</v>
+        <v>724.8318611344112</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>3175</v>
+        <v>480.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,49 +1400,49 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>49.77604157122526</v>
+        <v>54.77367478266825</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>18.22365294028608</v>
+        <v>31.86263219758136</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.9747381305289564</v>
+        <v>0.9196188655080628</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-20.97179481127575</v>
+        <v>0.8597318574979838</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6691</v>
+        <v>6742</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>澤米</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>601.6270775786942</v>
+        <v>712.0823499931538</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>686</v>
+        <v>61.1</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>47.3745121017835</v>
+        <v>61.39914539527489</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>26.56578014417374</v>
+        <v>54.65072691011976</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.4610714400794347</v>
+        <v>0.6082349993153824</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-6.299463171590897</v>
+        <v>0.1176895062576428</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6491</v>
+        <v>6805</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>晶碩</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>598.1217670856637</v>
+        <v>710.9564229187257</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>408.5</v>
+        <v>2335</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,49 +1506,49 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>54.63132238626566</v>
+        <v>53.53473628769922</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>30.03275393685355</v>
+        <v>28.19465015825555</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.7165139568369674</v>
+        <v>1.42538442685169</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-1.271727333700637</v>
+        <v>-34.78055190274878</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6668</v>
+        <v>6834</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>天二科技</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>586.2184607088543</v>
+        <v>701.2655830013466</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>61.5</v>
+        <v>133.5</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,49 +1559,49 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>64.67619756608892</v>
+        <v>55.45110200633057</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>56.44613391250201</v>
+        <v>50.87543436555298</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.284939289382922</v>
+        <v>0.6620833419162628</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>1.350230304548221</v>
+        <v>0.9646205765114786</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6645</v>
+        <v>6671</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>金萬林-創</t>
+          <t>三能-KY</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>570.2237865641223</v>
+        <v>686.9411698589694</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>14.3</v>
+        <v>23.45</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>59.6003039576825</v>
+        <v>59.20642265707733</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>30.72972225311729</v>
+        <v>14.71515663913517</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.8223786564122251</v>
+        <v>0.3971082705934816</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.2007454827341198</v>
+        <v>0.055567845642478</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6689</v>
+        <v>6743</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>567.3530281812483</v>
+        <v>686.8327475856544</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>69.2</v>
+        <v>31.85</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>63.71361917272751</v>
+        <v>50.94372422299009</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>28.30005050409402</v>
+        <v>31.16575398641573</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>6.062678370377307</v>
+        <v>0.8656646255588611</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.4954348573795211</v>
+        <v>-0.3393365600439126</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6517</v>
+        <v>6708</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>天擎</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>559</v>
+        <v>686.8160787271797</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>74.5</v>
+        <v>60.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>62.84350908661381</v>
+        <v>57.58667356442945</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>23.91494045357245</v>
+        <v>28.60303710647633</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>5.393906966793604</v>
+        <v>0.8302587811262123</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>1.163693839350791</v>
+        <v>-0.7845188951893078</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6743</v>
+        <v>6690</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>546.8327475856544</v>
+        <v>681.2023002004878</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>31.85</v>
+        <v>178</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>50.94372425793075</v>
+        <v>53.05065446590779</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>31.16575396368074</v>
+        <v>36.46855601873202</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.8656646255588611</v>
+        <v>0.6794931987498816</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.3393365601881239</v>
+        <v>-0.4863169873981161</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6533</v>
+        <v>6598</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>ABC-KY</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>544.1040020010443</v>
+        <v>668.8511236377617</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>295.5</v>
+        <v>28.9</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>48.83660490667858</v>
+        <v>57.63849115865666</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>28.85963643654425</v>
+        <v>15.79710714481663</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.5530962865556882</v>
+        <v>0.7651286168965549</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-5.084477049055341</v>
+        <v>0.2213980076453878</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6690</v>
+        <v>6655</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>科定</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>541.2023002004878</v>
+        <v>665.2918844074145</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>178</v>
+        <v>132.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>53.05065445414259</v>
+        <v>53.07479288394658</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>36.46855606037715</v>
+        <v>9.800751866999429</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.6794931987498816</v>
+        <v>1.890208174783305</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.4863169876384563</v>
+        <v>2.895234451482454</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6525</v>
+        <v>6658</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>533.7345882777926</v>
+        <v>660.0226363211235</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>125.5</v>
+        <v>201.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>36.81621729199283</v>
+        <v>59.31182316156166</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>13.40725432592836</v>
+        <v>37.3993929366527</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.7544776593876757</v>
+        <v>0.8688446598253142</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,51 +1948,51 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-1.020054140052673</v>
+        <v>0.0496644800527992</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6806</v>
+        <v>6667</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>信紘科</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>528.7768356926886</v>
+        <v>640.3494636238507</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>3.51</v>
+        <v>260</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="G29" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>31.69494412880849</v>
+        <v>50.52620980364184</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>32.59377477417976</v>
+        <v>38.86354706103089</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>2.013053626871306</v>
+        <v>0.537563030619216</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.4112809521672877</v>
+        <v>-1.531935496821882</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6588</v>
+        <v>6641</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>528.4096231781618</v>
+        <v>625.9037982991335</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>92.3</v>
+        <v>17.05</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>34.19094052824272</v>
+        <v>50.96124772557318</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>21.12581368320148</v>
+        <v>7.703770112226785</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.3398457757456075</v>
+        <v>0.4849883251729143</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-2.374213626900588</v>
+        <v>0.0357629363650511</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6693</v>
+        <v>6504</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>廣閎科</t>
+          <t>南六</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>525.6420560824861</v>
+        <v>623.6724918272862</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>170.5</v>
+        <v>39.75</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,49 +2089,49 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>39.36279694999636</v>
+        <v>54.9309299661324</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>19.43633706749121</v>
+        <v>46.00079711580734</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.4785975453785857</v>
+        <v>0.7672491827286197</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-4.120050550214538</v>
+        <v>0.1933623032915495</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6664</v>
+        <v>6695</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>517.7663794302958</v>
+        <v>607.4933384889852</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>340.5</v>
+        <v>51</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>38.72622860304027</v>
+        <v>52.08504873770672</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>18.09044275786512</v>
+        <v>19.0547614892076</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.683650664664767</v>
+        <v>4.058959488763687</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-3.784729088503251</v>
+        <v>-0.3431308010388743</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6742</v>
+        <v>6510</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>502.0823499931538</v>
+        <v>606.2123312282267</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>61.1</v>
+        <v>3175</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,49 +2195,49 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>61.39914530857185</v>
+        <v>49.77604159020003</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>54.65072687132625</v>
+        <v>18.22365295607135</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.6082349993153824</v>
+        <v>0.9747381305289564</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M33" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.1176895065220309</v>
+        <v>-20.97179481488111</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6598</v>
+        <v>6691</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>ABC-KY</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>498.8511236377613</v>
+        <v>601.6270775786942</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>28.9</v>
+        <v>686</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>57.6384911507937</v>
+        <v>47.374512131464</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>15.79710714481664</v>
+        <v>26.56578006302669</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.7651286168965549</v>
+        <v>0.4610714400794347</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.2213980076574043</v>
+        <v>-6.299463170028609</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6671</v>
+        <v>6792</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>三能-KY</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>496.9411698589692</v>
+        <v>590.8600887604404</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>23.45</v>
+        <v>59.1</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>59.20642236783499</v>
+        <v>48.37024740328417</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>14.71515640194398</v>
+        <v>37.72352778560756</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.3971082705934816</v>
+        <v>1.49155801550025</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.0555678456785293</v>
+        <v>-0.0451901487855724</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6655</v>
+        <v>6674</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>科定</t>
+          <t>鋐寶科技</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>495.2918844074144</v>
+        <v>584.7979779924997</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>132.5</v>
+        <v>18.35</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>53.07479288900186</v>
+        <v>68.7483810965703</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>9.800751861410051</v>
+        <v>44.21462193466659</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.890208174783305</v>
+        <v>0.1218302541194887</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>2.895234451362279</v>
+        <v>-0.0535665508254703</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6683</v>
+        <v>6561</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>雍智科技</t>
+          <t>是方</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>483.360593785778</v>
+        <v>571.7773118965259</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>1275</v>
+        <v>312.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,49 +2407,49 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>40.46109562379571</v>
+        <v>49.0479625230208</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>14.43399656341437</v>
+        <v>16.7606334508353</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.4350155659707319</v>
+        <v>1.168075745209411</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M37" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-33.83375870305171</v>
+        <v>0.3776650590213548</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, invest_trust_buy_2d</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6654</v>
+        <v>6485</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>460.2614656384332</v>
+        <v>558.352430539982</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>200</v>
+        <v>76.8</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>46.49112477305519</v>
+        <v>54.22558706001163</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>27.58088885584624</v>
+        <v>34.8569661606807</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.8163697520867074</v>
+        <v>0.3527086135252613</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-2.371646557116637</v>
+        <v>-0.4013933536001985</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6504</v>
+        <v>6768</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>志強-KY</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>453.6724918272862</v>
+        <v>557.1103685095907</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>39.75</v>
+        <v>63.4</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>54.93092983611436</v>
+        <v>46.7330251208156</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>46.00079707172471</v>
+        <v>23.50760118424834</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.7672491827286197</v>
+        <v>1.060900327657544</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.1933623035439159</v>
+        <v>0.1886280120811875</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6530</v>
+        <v>6534</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>正瀚-創</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>441.0029041559844</v>
+        <v>556.2103446293</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>91.8</v>
+        <v>92</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>45.0967619458341</v>
+        <v>47.7798159907864</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>22.59453624088362</v>
+        <v>25.88977139158539</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.2020840171060429</v>
+        <v>0.6332569807653343</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-1.194630448421158</v>
+        <v>0.0507742438652801</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6805</v>
+        <v>6530</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>440.9564229187258</v>
+        <v>556.0029041559843</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>2335</v>
+        <v>91.8</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>53.5347362841549</v>
+        <v>45.09676200655686</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>28.19465015926705</v>
+        <v>22.59453621365165</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.42538442685169</v>
+        <v>0.2020840171060429</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-34.78055190395068</v>
+        <v>-1.194630448541329</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6669</v>
+        <v>6556</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>439.3908273490872</v>
+        <v>554.1637915081055</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>1885</v>
+        <v>63.3</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>27.55434221116624</v>
+        <v>52.97733769253327</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>43.32971874532107</v>
+        <v>22.94646282679561</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.381679941637639</v>
+        <v>0.6106962761830876</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>88.91358531412311</v>
+        <v>0.3560294768067227</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6695</v>
+        <v>6581</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>437.4933384889845</v>
+        <v>548.8774898507802</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>51</v>
+        <v>108.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,49 +2725,49 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>52.0850489840082</v>
+        <v>49.32360943711257</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>19.05476147447872</v>
+        <v>20.09031340321675</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>4.058959488763687</v>
+        <v>3.077588886309718</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.343130802192537</v>
+        <v>-0.0024254005172321</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6485</v>
+        <v>6533</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>418.3524305399793</v>
+        <v>544.1040020010443</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>76.8</v>
+        <v>295.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,49 +2778,49 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>54.22558707100008</v>
+        <v>48.83660493022924</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>34.85696612683533</v>
+        <v>28.85963648370436</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.3527086135252613</v>
+        <v>0.5530962865556882</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.4013933538405547</v>
+        <v>-5.084477047853646</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6768</v>
+        <v>6525</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>志強-KY</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>417.1103685095907</v>
+        <v>533.7345882777923</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>63.4</v>
+        <v>125.5</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>46.73302484711829</v>
+        <v>36.81621729775461</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>23.50760122951776</v>
+        <v>13.40725436589338</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.060900327657544</v>
+        <v>0.7544776593876757</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,84 +2849,84 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.1886280123215355</v>
+        <v>-1.020054140004574</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6584</v>
+        <v>6806</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>416.3310184472937</v>
+        <v>528.7768356926886</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>472.5</v>
+        <v>3.51</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G46" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>31.90987950342456</v>
+        <v>31.69497308232388</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>25.46607668985216</v>
+        <v>32.5937420565275</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.7604627057660253</v>
+        <v>2.013053626871306</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-5.727400551633494</v>
+        <v>0.4112806336488819</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6534</v>
+        <v>6588</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>正瀚-創</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>416.2103446293004</v>
+        <v>528.4096231781618</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>92</v>
+        <v>92.3</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>47.77981602362699</v>
+        <v>34.19094052966106</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>25.88977139302467</v>
+        <v>21.12581372769615</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.6332569807653343</v>
+        <v>0.3398457757456075</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.0507742436249367</v>
+        <v>-2.37421362692463</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6674</v>
+        <v>6693</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>鋐寶科技</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>414.7979779924997</v>
+        <v>525.6420560824861</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>18.35</v>
+        <v>170.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,49 +2990,49 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>68.74838048527829</v>
+        <v>39.36279695106115</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>44.21462158748189</v>
+        <v>19.43633709421237</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.1218302541194887</v>
+        <v>0.4785975453785857</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.053566550488982</v>
+        <v>-4.120050550214538</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6741</v>
+        <v>6722</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>406</v>
+        <v>520.6522166991459</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>49.2</v>
+        <v>32.95</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>17.36001402103602</v>
+        <v>51.08719314316956</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>36.51431959827707</v>
+        <v>33.91395938803318</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>5.708737947274456</v>
+        <v>0.9201700669479964</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.3924669294469847</v>
+        <v>0.037485244221595</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6579</v>
+        <v>6577</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>405.6413020281218</v>
+        <v>518.469198020776</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>143</v>
+        <v>79</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>33.18388957328229</v>
+        <v>43.46973783598197</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>22.31020597221097</v>
+        <v>10.68593692882478</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.9458615705987872</v>
+        <v>0.8849972160311677</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-1.259997303576367</v>
+        <v>-0.1258531925802802</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6561</v>
+        <v>6664</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>401.7773118965261</v>
+        <v>517.7663794302953</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>312.5</v>
+        <v>340.5</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,49 +3149,49 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>49.04796256230443</v>
+        <v>38.72622858506369</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>16.76063351249762</v>
+        <v>18.09044264510674</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.168075745209411</v>
+        <v>0.683650664664767</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.3776650601029505</v>
+        <v>-3.784729087301518</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6831</v>
+        <v>6592</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>和潤企業</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>400.6508127435384</v>
+        <v>488.0431717686564</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>407.5</v>
+        <v>56.8</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>26.5408927523186</v>
+        <v>40.54763079010861</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>32.72936706442334</v>
+        <v>27.08132878481818</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.9650812743538444</v>
+        <v>0.5154700796599465</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-4.459634998031426</v>
+        <v>0.183351856162087</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6716</v>
+        <v>6683</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>應廣</t>
+          <t>雍智科技</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>397.6615258147641</v>
+        <v>483.3605937857777</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>90.7</v>
+        <v>1275</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,49 +3255,49 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>33.80836915150252</v>
+        <v>40.46109559495905</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>27.89902113172257</v>
+        <v>14.43399656424625</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.5534910532883272</v>
+        <v>0.4350155659707319</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M53" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-4.713965695043866</v>
+        <v>-33.83375869367809</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6556</v>
+        <v>6670</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>384.1637915081057</v>
+        <v>482.2622196025117</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>63.3</v>
+        <v>265</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>52.97733765430519</v>
+        <v>42.36020438344586</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>22.94646280572138</v>
+        <v>16.97399844737164</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.6106962761830876</v>
+        <v>1.647033884106418</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.3560294766625126</v>
+        <v>-0.6425791923059441</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6722</v>
+        <v>6807</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>峰源-KY</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>380.6522166991459</v>
+        <v>479.0559340529183</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>32.95</v>
+        <v>33.75</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>51.08719289335451</v>
+        <v>51.99434272244838</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>33.9139593650732</v>
+        <v>10.11775958562085</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.9201700669479964</v>
+        <v>0.3031604476669277</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0374852441254584</v>
+        <v>0.9767358561562351</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6581</v>
+        <v>6605</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>378.8774898507802</v>
+        <v>472.5029993638473</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>108.5</v>
+        <v>136</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>49.32360949120503</v>
+        <v>46.82560634704638</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>20.09031325164018</v>
+        <v>10.80154834396366</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>3.077588886309718</v>
+        <v>1.153141507390872</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.0024254006374155</v>
+        <v>-0.0236247710385936</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6761</v>
+        <v>6669</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>穩得</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>378.7730246192712</v>
+        <v>460.515039431322</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>148.5</v>
+        <v>1885</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>29.16894149100416</v>
+        <v>27.55434218679128</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>21.29149049595769</v>
+        <v>43.32971877899029</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.089130285490906</v>
+        <v>1.467485566841637</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-1.573925379148369</v>
+        <v>88.91358531532467</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6577</v>
+        <v>6654</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>天正國際</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>378.4691980207761</v>
+        <v>460.2614656384334</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>79</v>
+        <v>200</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>43.46973777480311</v>
+        <v>46.49112479239763</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>10.68593679562885</v>
+        <v>27.58088898897729</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.8849972160311677</v>
+        <v>0.8163697520867074</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.1258531923879975</v>
+        <v>-2.371646557477163</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6641</v>
+        <v>6692</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>375.9037982991336</v>
+        <v>459.5611990591415</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>17.05</v>
+        <v>22.35</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>50.96124766415506</v>
+        <v>49.25346657376608</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>7.703769981817083</v>
+        <v>5.829425861854149</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.4849883251729143</v>
+        <v>0.387226174056027</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.035762936437156</v>
+        <v>-0.0208433956644686</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6830</v>
+        <v>6582</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>汎銓</t>
+          <t>申豐</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>366.0947826769538</v>
+        <v>452.4210159358079</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>491.5</v>
+        <v>31.65</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>39.95299441926255</v>
+        <v>51.62154800102167</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>20.42426886575042</v>
+        <v>19.6539317511957</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.974798115312972</v>
+        <v>0.716106756231672</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-8.086069120172992</v>
+        <v>0.07971383595195961</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6770</v>
+        <v>6719</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>363.3125966699797</v>
+        <v>439.3500226291299</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>65.3</v>
+        <v>178.5</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>39.5147978769835</v>
+        <v>40.07776518047486</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>12.46986404468296</v>
+        <v>13.96640826413989</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.936996365392776</v>
+        <v>1.06106332063731</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-1.031737989947681</v>
+        <v>-0.2892405195644008</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6640</v>
+        <v>6835</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>圓裕</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>356.5554616029888</v>
+        <v>439.2635317544164</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>985</v>
+        <v>31.9</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>41.13354649575532</v>
+        <v>53.25900055297943</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>17.53239955529249</v>
+        <v>19.70410233737769</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.5555461602988834</v>
+        <v>0.2627312586889103</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-13.49285684357195</v>
+        <v>0.0403562785391676</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6789</v>
+        <v>6550</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>北極星藥業-KY</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>353.145402836856</v>
+        <v>436.9117269958242</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>435</v>
+        <v>15.55</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>37.63536021892526</v>
+        <v>59.59075204463451</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>18.05855426618336</v>
+        <v>34.34396221032296</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.8224586682131145</v>
+        <v>0.3607672651161195</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-5.740975280557596</v>
+        <v>-0.0497026724823435</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6488</v>
+        <v>6591</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>346.1015986023455</v>
+        <v>436.7704394727339</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>882</v>
+        <v>41.55</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>37.3618161456377</v>
+        <v>40.39328334029544</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>19.10113883531409</v>
+        <v>29.23008016613317</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.8101598602345441</v>
+        <v>1.204548245818982</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-26.46396201507584</v>
+        <v>-0.07584825372119421</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6558</v>
+        <v>6642</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>興能高</t>
+          <t>富致</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>343.7008518122662</v>
+        <v>434.5480905861601</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>23.1</v>
+        <v>72.8</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>35.67725294402453</v>
+        <v>35.81063635953602</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>20.99998658730517</v>
+        <v>17.4767586652409</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.6575264942056243</v>
+        <v>0.7227521827499196</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.1676385941091118</v>
+        <v>-0.7961584122531213</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6670</v>
+        <v>6486</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>342.2622196025117</v>
+        <v>428.8295311247573</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>265</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>42.36020432646827</v>
+        <v>49.6728641962024</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>16.97399843014507</v>
+        <v>26.93315898227272</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.647033884106418</v>
+        <v>1.989575263602176</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.6425791919454648</v>
+        <v>-0.1526816113985624</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6792</v>
+        <v>6494</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>340.8600887604387</v>
+        <v>427.4784681983379</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>59.1</v>
+        <v>47.45</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>48.37024748841513</v>
+        <v>32.49900066475126</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>37.72352772975072</v>
+        <v>15.53908209721975</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.49155801550025</v>
+        <v>0.8332887953362551</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.0451901493383702</v>
+        <v>-0.4168644903959047</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6799</v>
+        <v>6698</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>334.4324746623237</v>
+        <v>426.558428741384</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>82.59999999999999</v>
+        <v>31.5</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>40.0314004733544</v>
+        <v>49.20600167431344</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>26.17632255179776</v>
+        <v>10.60633298134378</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.4924385706634653</v>
+        <v>1.104957925313369</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.9657128309830548</v>
+        <v>-0.0568929983318785</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6719</v>
+        <v>6771</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>平和環保-創</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>324.3500226291299</v>
+        <v>422.9342188670968</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>178.5</v>
+        <v>40.2</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>40.07776519190437</v>
+        <v>36.00961556667679</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>13.96640821201609</v>
+        <v>18.80150560176675</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.06106332063731</v>
+        <v>0.434189765256835</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.289240520165265</v>
+        <v>-0.2891907991769037</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6550</v>
+        <v>6585</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>北極星藥業-KY</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>321.9117269958242</v>
+        <v>421.3212350472018</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>15.55</v>
+        <v>97.2</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>59.59075195409616</v>
+        <v>33.90330166802495</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>34.34396234336539</v>
+        <v>35.39909854701553</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.3607672651161195</v>
+        <v>0.9975228981830236</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.0497026720246651</v>
+        <v>-0.1890335244539596</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6692</v>
+        <v>6831</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>邁科</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>319.5611990591415</v>
+        <v>420.6508127435384</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>22.35</v>
+        <v>407.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>49.25346657376608</v>
+        <v>26.54089272814069</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>5.8294257425604</v>
+        <v>32.72936718341819</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.387226174056027</v>
+        <v>0.9650812743538444</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>2</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.0208433956644686</v>
+        <v>-4.459634996949767</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6642</v>
+        <v>6614</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>富致</t>
+          <t>資拓宏宇</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>319.5480905861602</v>
+        <v>417.1286943394689</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>72.8</v>
+        <v>34.75</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>35.81063632144816</v>
+        <v>36.20917427079252</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>17.47675870799971</v>
+        <v>21.25830392087565</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.7227521827499196</v>
+        <v>1.451104287407311</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.796158412229087</v>
+        <v>-0.0258023883391404</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6494</v>
+        <v>6776</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>312.4784681983393</v>
+        <v>417.0743680922567</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>47.45</v>
+        <v>52.3</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>32.49900077671482</v>
+        <v>46.52318733806805</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>15.53908217636119</v>
+        <v>10.48145873295788</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.8332887953362551</v>
+        <v>0.6934289559386415</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.416864490600201</v>
+        <v>0.0370502506361525</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6582</v>
+        <v>6584</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>申豐</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>312.4210159358093</v>
+        <v>416.3310184472938</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>31.65</v>
+        <v>472.5</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,49 +4368,49 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>51.62154819696973</v>
+        <v>31.90987951606853</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>19.6539317515083</v>
+        <v>25.46607670262751</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.716106756231672</v>
+        <v>0.7604627057660253</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.07971383585582011</v>
+        <v>-5.727400546586097</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6725</v>
+        <v>6741</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>310.0199710343516</v>
+        <v>406</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>186</v>
+        <v>49.2</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>25.67063546666661</v>
+        <v>17.36001397274801</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>19.22261624521636</v>
+        <v>36.51431972603172</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.538401526866441</v>
+        <v>5.708737947274456</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-2.391157386799454</v>
+        <v>-0.3924669293748815</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6807</v>
+        <v>6579</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>峰源-KY</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>309.0559340529203</v>
+        <v>405.6413020281218</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>33.75</v>
+        <v>143</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>51.99434273652427</v>
+        <v>33.18388980459609</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>10.11775944799056</v>
+        <v>22.31020599865078</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.3031604476669277</v>
+        <v>0.9458615705987872</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.9767358559759752</v>
+        <v>-1.259997303095697</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6771</v>
+        <v>6732</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>平和環保-創</t>
+          <t>昇佳電子</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>307.9342188670968</v>
+        <v>405.4310635681822</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>40.2</v>
+        <v>149</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>36.00961555584605</v>
+        <v>44.27470022738301</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>18.80150559056792</v>
+        <v>16.74776587588532</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.434189765256835</v>
+        <v>1.696755801107898</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.2891907991528635</v>
+        <v>0.1039499294037376</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6643</v>
+        <v>6716</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>應廣</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>300.2017004823442</v>
+        <v>397.6615258147641</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>443.5</v>
+        <v>90.7</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>44.04505398247103</v>
+        <v>33.80836915150252</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>24.94172056110641</v>
+        <v>27.89902113172257</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.3477827007077439</v>
+        <v>0.5534910532883272</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-8.914399718992238</v>
+        <v>-4.713965695043866</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6835</v>
+        <v>6606</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>建德工業</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>299.2635317544164</v>
+        <v>394.917434050587</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>31.9</v>
+        <v>24.05</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>53.25900053607871</v>
+        <v>39.86267495129625</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>19.70410196584844</v>
+        <v>26.45140587286052</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.2627312586889103</v>
+        <v>1.049879482343043</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.0403562785391676</v>
+        <v>-0.0147314994001019</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6591</v>
+        <v>6568</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>宏觀</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>296.7704394727317</v>
+        <v>394.9069693594357</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>41.55</v>
+        <v>135</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>40.39328327091065</v>
+        <v>48.24874330926088</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>29.23008030544841</v>
+        <v>15.53449973529315</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.204548245818982</v>
+        <v>0.8491123242424938</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.0758482540336462</v>
+        <v>-0.3643845517646418</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6829</v>
+        <v>6803</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>千附精密</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>293.8817373230806</v>
+        <v>391.2419616298336</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>191.5</v>
+        <v>260</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>37.8937131829379</v>
+        <v>32.39504578581261</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>13.22537372453267</v>
+        <v>25.17333883573095</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.4485082327166742</v>
+        <v>1.020726993575845</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-1.623281514730692</v>
+        <v>-0.3909941815163942</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6605</v>
+        <v>6821</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>聯寶</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>292.5029993638474</v>
+        <v>386.3441215317624</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>136</v>
+        <v>43.25</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>46.82560640068172</v>
+        <v>49.16630491646025</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>10.80154834396365</v>
+        <v>25.18432523008489</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.153141507390872</v>
+        <v>0.3900243969964528</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.0236247715192974</v>
+        <v>0.0227877726658953</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6585</v>
+        <v>6830</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>鼎基</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>281.3212350472018</v>
+        <v>386.0947826769538</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>97.2</v>
+        <v>491.5</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>33.90330141737238</v>
+        <v>39.95299442558595</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>35.39909853174273</v>
+        <v>20.42426885685612</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.9975228981830236</v>
+        <v>0.974798115312972</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.1890335244299144</v>
+        <v>-8.086069119812489</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6614</v>
+        <v>6757</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>資拓宏宇</t>
+          <t>台灣虎航-創</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>277.1286943394678</v>
+        <v>386.0488245960185</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>34.75</v>
+        <v>53.1</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,29 +4898,29 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>36.20917345316461</v>
+        <v>43.5574768193523</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>21.25830392087564</v>
+        <v>12.48670943082999</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.451104287407311</v>
+        <v>1.982639536636197</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.025802388291067</v>
+        <v>0.1152465785883526</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>268.5736116507306</v>
+        <v>383.5736116507305</v>
       </c>
       <c r="E85" s="2" t="n">
         <v>121.5</v>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>24.66878586436469</v>
+        <v>24.66878555738733</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>22.17223877963652</v>
+        <v>22.17223874426517</v>
       </c>
       <c r="J85" s="2" t="n">
         <v>0.7218675958114958</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,11 +4969,11 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.8706528465073489</v>
+        <v>-0.8706528435030441</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
@@ -4990,7 +4990,7 @@
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>266.1358556142999</v>
+        <v>381.1358556142999</v>
       </c>
       <c r="E86" s="2" t="n">
         <v>821</v>
@@ -5004,10 +5004,10 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>38.85636070455421</v>
+        <v>38.856360712316</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>15.65482958563884</v>
+        <v>15.65482956278917</v>
       </c>
       <c r="J86" s="2" t="n">
         <v>1.013585561429986</v>
@@ -5016,37 +5016,37 @@
         <v>0</v>
       </c>
       <c r="L86" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M86" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-19.69647158568338</v>
+        <v>-19.69647158544308</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6732</v>
+        <v>6761</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>昇佳電子</t>
+          <t>穩得</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>265.4310635681821</v>
+        <v>378.7730246192712</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>149</v>
+        <v>148.5</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>44.27470001637463</v>
+        <v>29.16894165961787</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>16.74776584862174</v>
+        <v>21.29149048633852</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.696755801107898</v>
+        <v>1.089130285490906</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.1039499290432006</v>
+        <v>-1.573925377465957</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6486</v>
+        <v>6684</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>258.8295311247572</v>
+        <v>371.3106399623197</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>79.09999999999999</v>
+        <v>45.7</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>49.67286415388812</v>
+        <v>39.33589382827002</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>26.93315903983792</v>
+        <v>20.60203202478766</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.989575263602176</v>
+        <v>0.3846793081401997</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.1526816112543571</v>
+        <v>-0.4360179448631212</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6515</v>
+        <v>6624</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>萬年清</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>257.212504762314</v>
+        <v>368.4286504001627</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>5160</v>
+        <v>37.7</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>37.48922176973425</v>
+        <v>51.47485789503274</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>12.45161425126073</v>
+        <v>7.239909679074397</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.6383045481962877</v>
+        <v>0.424375691536296</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-61.87056404577169</v>
+        <v>-1.57095084271647</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6684</v>
+        <v>6754</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>256.3106399623176</v>
+        <v>366.6355753760504</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>45.7</v>
+        <v>40.5</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>39.33589382827002</v>
+        <v>41.44419999511709</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>20.60203198681995</v>
+        <v>17.32503523496634</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.3846793081401997</v>
+        <v>1.732882783809543</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.4360179457283683</v>
+        <v>-0.0789632909125931</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6803</v>
+        <v>6770</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>251.2419616298329</v>
+        <v>363.3125966699797</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>260</v>
+        <v>65.3</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,29 +5269,29 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>32.39504564578121</v>
+        <v>39.51479787884404</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>25.17333885594302</v>
+        <v>12.46986410222558</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.020726993575845</v>
+        <v>0.936996365392776</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.3909941807953225</v>
+        <v>-1.031737989947681</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>247.4525345062774</v>
+        <v>362.4525345062773</v>
       </c>
       <c r="E92" s="2" t="n">
         <v>59.1</v>
@@ -5322,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>43.12663686565476</v>
+        <v>43.12663689222369</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>12.18475103890676</v>
+        <v>12.18475122943671</v>
       </c>
       <c r="J92" s="2" t="n">
         <v>1.030570532906101</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.0014734459613134</v>
+        <v>0.0014734467304197</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6821</v>
+        <v>6651</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>聯寶</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>246.3441215317766</v>
+        <v>361.6648000138048</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>43.25</v>
+        <v>139.5</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>49.16630505105231</v>
+        <v>43.53715725298333</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>25.18432519092753</v>
+        <v>13.15234996824613</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.3900243969964528</v>
+        <v>0.6940820671400967</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.022787772677921</v>
+        <v>-1.199478018559014</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6757</v>
+        <v>6640</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>台灣虎航-創</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>246.0488245960188</v>
+        <v>356.5554616029888</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>53.1</v>
+        <v>985</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>43.5574768193523</v>
+        <v>41.13354648508356</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>12.48670943083</v>
+        <v>17.53239951555041</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.982639536636197</v>
+        <v>0.5555461602988834</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.1152465786844854</v>
+        <v>-13.49285684212963</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6739</v>
+        <v>6560</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>238.7541133758171</v>
+        <v>355.8954255873222</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>906</v>
+        <v>32</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>33.72316576585447</v>
+        <v>48.99384306916212</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>13.72511318939002</v>
+        <v>9.819236241641706</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.312655498804098</v>
+        <v>0.0534430331280914</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-22.95229892289398</v>
+        <v>-0.1635182747564099</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6573</v>
+        <v>6789</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>虹揚-KY</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>237.0780061117027</v>
+        <v>353.145402836852</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>15</v>
+        <v>435</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>34.19701277184993</v>
+        <v>37.63536017786003</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>13.76251331599384</v>
+        <v>18.05855424634574</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.7005339234639504</v>
+        <v>0.8224586682131145</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.0649760441302521</v>
+        <v>-5.740975278875155</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6698</v>
+        <v>6498</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>236.5584287413807</v>
+        <v>349.804944700974</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>31.5</v>
+        <v>66.7</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>49.20600175790195</v>
+        <v>42.09259629681921</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>10.60633300159688</v>
+        <v>13.95562252253667</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1.104957925313369</v>
+        <v>0.656045934993653</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.0568929984881039</v>
+        <v>-0.0077222058900635</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6781</v>
+        <v>6488</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>235.5667639163013</v>
+        <v>346.2334745053486</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>935</v>
+        <v>882</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>34.67623752724899</v>
+        <v>37.36181612992118</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>18.83474037607461</v>
+        <v>19.10113883133232</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.6000852282478536</v>
+        <v>0.8233474505348573</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-7.699369016201835</v>
+        <v>-26.46396201315309</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6606</v>
+        <v>6558</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>建德工業</t>
+          <t>興能高</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>234.917434050587</v>
+        <v>343.7008518122666</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>24.05</v>
+        <v>23.1</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>39.86267485062772</v>
+        <v>35.67725360498832</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>26.4514059959615</v>
+        <v>20.99998661508898</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.049879482343043</v>
+        <v>0.6575264942056243</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.0147314995322918</v>
+        <v>-0.1676385943013886</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6498</v>
+        <v>6823</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>濾能</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>234.804944700974</v>
+        <v>341.0695520806456</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>66.7</v>
+        <v>59.2</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>42.09259620108745</v>
+        <v>43.30901106529267</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>13.95562248957994</v>
+        <v>16.83095067997231</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.656045934993653</v>
+        <v>2.214694446193565</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.0077222056497174</v>
+        <v>-0.0275442254215824</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6754</v>
+        <v>6666</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>羅麗芬-KY</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>231.6355753760505</v>
+        <v>340.5169681540968</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>40.5</v>
+        <v>42.2</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>41.44419955549519</v>
+        <v>34.41975524413199</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>17.32503523496634</v>
+        <v>24.57939687459206</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.732882783809543</v>
+        <v>1.297037664532386</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.0789632909125931</v>
+        <v>-0.3491911530050811</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6666</v>
+        <v>6796</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>羅麗芬-KY</t>
+          <t>晉弘</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>225.5169681540968</v>
+        <v>340.371969661601</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>42.2</v>
+        <v>53.4</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>34.41975670032716</v>
+        <v>43.34864091170105</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>24.57939641888637</v>
+        <v>15.99390221169686</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.297037664532386</v>
+        <v>0.6855342019986447</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.3491911543510244</v>
+        <v>0.1189627612874686</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6796</v>
+        <v>6790</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>晉弘</t>
+          <t>永豐實</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>225.371969661601</v>
+        <v>340.1563277474126</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>53.4</v>
+        <v>37.6</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>43.34864091170105</v>
+        <v>46.37459015223291</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>15.99390219410048</v>
+        <v>17.98009964369351</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.6855342019986447</v>
+        <v>1.082842477138682</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.1189627612634318</v>
+        <v>0.0568569143989133</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6568</v>
+        <v>6625</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>宏觀</t>
+          <t>必應</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>224.9069693594357</v>
+        <v>335.5002043429036</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>135</v>
+        <v>72.7</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>48.24874326431252</v>
+        <v>39.52157857908841</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>15.53449973736909</v>
+        <v>12.59147264825467</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.8491123242424938</v>
+        <v>0.6783857918948053</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.3643845521251882</v>
+        <v>-0.0274951683749762</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6651</v>
+        <v>6799</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>221.6648000138047</v>
+        <v>334.4324746623237</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>139.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>43.53715721782518</v>
+        <v>40.03140048967007</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>13.15235004512112</v>
+        <v>26.17632253908156</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.6940820671400967</v>
+        <v>0.4924385706634653</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-1.199478018583051</v>
+        <v>-0.9657128305984934</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6560</v>
+        <v>6570</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>215.8954255873223</v>
+        <v>332.5960381620849</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>32</v>
+        <v>46.65</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>48.99384312514263</v>
+        <v>39.41858937317961</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>9.819236228151077</v>
+        <v>19.63746440343867</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.0534430331280914</v>
+        <v>0.5076142131979695</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,11 +6082,11 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.1635182747804457</v>
+        <v>0.1278203280987</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>208.758775345478</v>
+        <v>323.7587753454777</v>
       </c>
       <c r="E107" s="2" t="n">
         <v>186.5</v>
@@ -6117,10 +6117,10 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>34.43229769570165</v>
+        <v>34.43229758752631</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>15.39667731930491</v>
+        <v>15.39667732923619</v>
       </c>
       <c r="J107" s="2" t="n">
         <v>1.10157226703786</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-1.178353002752216</v>
+        <v>-1.178353001310156</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6592</v>
+        <v>6788</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>和潤企業</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>208.0431717686564</v>
+        <v>322.3108197034577</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>56.8</v>
+        <v>353.5</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>40.54763074453373</v>
+        <v>48.33126129798774</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>27.08132870379487</v>
+        <v>18.49034146723112</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.5154700796599465</v>
+        <v>0.6248504678512709</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.183351856330333</v>
+        <v>0.0332029254814276</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6788</v>
+        <v>6552</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>易華電</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>207.3108197034577</v>
+        <v>318.8446837451792</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>353.5</v>
+        <v>23.2</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>48.33126133628043</v>
+        <v>36.64129414365569</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>18.49034134550095</v>
+        <v>18.31313784488822</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.6248504678512709</v>
+        <v>0.9493947829253911</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0332029237990108</v>
+        <v>-0.1334233847676569</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6823</v>
+        <v>6589</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>濾能</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>201.0695520806456</v>
+        <v>317.026336469399</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>59.2</v>
+        <v>48.8</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>43.30901129306841</v>
+        <v>44.38748482255326</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>16.83095064891297</v>
+        <v>19.15149383882493</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>2.214694446193565</v>
+        <v>0.7229021364384183</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.0275442258782417</v>
+        <v>-0.2925031315212869</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6624</v>
+        <v>6725</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>萬年清</t>
+          <t>矽科宏晟</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>198.4286504001626</v>
+        <v>310.0199710343549</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>37.7</v>
+        <v>186</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>51.47485762063391</v>
+        <v>25.67063505999306</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>7.239909677130816</v>
+        <v>19.22261635488427</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.424375691536296</v>
+        <v>1.538401526866441</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-1.57095084271647</v>
+        <v>-2.391157383194265</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6570</v>
+        <v>6643</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>192.596038162085</v>
+        <v>300.2017004823444</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>46.65</v>
+        <v>443.5</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>39.41858995846499</v>
+        <v>44.04505390776784</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>19.6374642111144</v>
+        <v>24.9417207697153</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.5076142131979695</v>
+        <v>0.3477827007077439</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.1278203270892468</v>
+        <v>-8.914399713584441</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6552</v>
+        <v>6829</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>易華電</t>
+          <t>千附精密</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>183.8446837451795</v>
+        <v>293.8817373230806</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>23.2</v>
+        <v>191.5</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>36.64129427880403</v>
+        <v>37.89371313517395</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>18.31313765477507</v>
+        <v>13.22537385709652</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.9493947829253911</v>
+        <v>0.4485082327166742</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.1334233849118661</v>
+        <v>-1.623281513168459</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6597</v>
+        <v>6763</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>181.3735607955037</v>
+        <v>289.6231392418646</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>0</v>
+        <v>40.85</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>42.81639957634585</v>
+        <v>41.73880214619235</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>8.028911181404347</v>
+        <v>13.94394250197259</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.0007667792873744</v>
+        <v>1.399510297118529</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-4.684734300705486</v>
+        <v>-0.0044144022887666</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6735</v>
+        <v>6794</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>美達科技</t>
+          <t>向榮生技-創</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>178.4168846195862</v>
+        <v>288.9892801326383</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>58.2</v>
+        <v>69.3</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>35.31368774762527</v>
+        <v>37.66462646373287</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>16.3264070718704</v>
+        <v>13.99087815837617</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.7550297485093318</v>
+        <v>0.8415944906735611</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.6578207246523047</v>
+        <v>-0.4594022185998498</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6589</v>
+        <v>6512</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>177.026336469399</v>
+        <v>275.8987254467285</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>48.8</v>
+        <v>20.1</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>44.38748494521733</v>
+        <v>51.85633363068696</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>19.15149375831278</v>
+        <v>7.75710636380053</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.7229021364384183</v>
+        <v>0.8926258891537321</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.2925031317616356</v>
+        <v>0.333917397335435</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6790</v>
+        <v>6515</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>永豐實</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>170.1563277474126</v>
+        <v>267.212504762314</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>37.6</v>
+        <v>5160</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,16 +6647,16 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>46.37459015223291</v>
+        <v>37.48922180253238</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>17.98009958220736</v>
+        <v>12.45161421765934</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.082842477138682</v>
+        <v>0.6383045481962877</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.0568569144109257</v>
+        <v>-61.87056404336784</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6776</v>
+        <v>6781</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>167.0743680922568</v>
+        <v>255.5667639163013</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>52.3</v>
+        <v>935</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>46.52318699248457</v>
+        <v>34.67623738477765</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>10.48145880254201</v>
+        <v>18.83474031998256</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.6934289559386415</v>
+        <v>0.6000852282478536</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.0370502508284327</v>
+        <v>-7.69936901019318</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6541</v>
+        <v>6680</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>泰福-KY</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>150.4493318260942</v>
+        <v>247.5099389613386</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>30.05</v>
+        <v>48.5</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>41.90744078913681</v>
+        <v>51.47050481616496</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>16.69797732985652</v>
+        <v>6.024253944282402</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.4501079065898562</v>
+        <v>0.2497114936037518</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.021144805945318</v>
+        <v>1.416557867216083</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6763</v>
+        <v>6739</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>149.6231392418607</v>
+        <v>238.7541133758172</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>40.85</v>
+        <v>906</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>41.73880188803263</v>
+        <v>33.72316572900617</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>13.94394251598444</v>
+        <v>13.72511318350023</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>1.399510297118529</v>
+        <v>1.312655498804098</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.0044144021445585</v>
+        <v>-22.95229892145186</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6794</v>
+        <v>6573</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>向榮生技-創</t>
+          <t>虹揚-KY</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>148.9892801326382</v>
+        <v>237.0780061117028</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>69.3</v>
+        <v>15</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>37.66462648512949</v>
+        <v>34.19701265454809</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>13.99087832974306</v>
+        <v>13.76251333561865</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.8415944906735611</v>
+        <v>0.7005339234639504</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.4594022185998498</v>
+        <v>-0.0649760440821819</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6720</v>
+        <v>6477</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>安集</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>136.9052403905072</v>
+        <v>207.9089124691698</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>100</v>
+        <v>32.1</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>38.92142672827014</v>
+        <v>37.44315954589111</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>18.18988721384568</v>
+        <v>14.88507005990922</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.3566536910999996</v>
+        <v>0.3271596487529297</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-2.297473144181783</v>
+        <v>-0.1653508712829876</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6512</v>
+        <v>6597</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>135.8987254467285</v>
+        <v>181.3735607955037</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>20.1</v>
+        <v>0</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>51.85633363294835</v>
+        <v>42.81639956944657</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>7.757106366806542</v>
+        <v>8.028911215912414</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.8926258891537321</v>
+        <v>0.0007667792873744</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.3339173973234181</v>
+        <v>-4.684734300441113</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6680</v>
+        <v>6735</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>美達科技</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>132.5099389613386</v>
+        <v>178.4168846195836</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>48.5</v>
+        <v>58.2</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>51.4705048071361</v>
+        <v>35.3136880132212</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>6.024253944962159</v>
+        <v>16.32640707511782</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.2497114936037518</v>
+        <v>0.7550297485093318</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>1.416557867312218</v>
+        <v>-0.6578207244960834</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>6625</v>
+        <v>6541</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>必應</t>
+          <t>泰福-KY</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>110.5002043429044</v>
+        <v>150.4493318260942</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>72.7</v>
+        <v>30.05</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>39.52157854141746</v>
+        <v>41.90744077466596</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>12.59147264825468</v>
+        <v>16.69797732665035</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.6783857918948053</v>
+        <v>0.4501079065898562</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.0274951682307601</v>
+        <v>0.021144805969348</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>6477</v>
+        <v>6720</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>安集</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>92.90891246916992</v>
+        <v>136.9052403905072</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>32.1</v>
+        <v>100</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,16 +7124,16 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>37.44316004025071</v>
+        <v>38.92142674073951</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>14.88507013724579</v>
+        <v>18.18988727954536</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.3271596487529297</v>
+        <v>0.3566536910999996</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L126" s="2" t="n">
         <v>0</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.1653508720520908</v>
+        <v>-2.297473144181783</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
